--- a/documents/LoRa-E5 Pinout.xlsx
+++ b/documents/LoRa-E5 Pinout.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repo\fw_LoRaMesher\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFC29760-9F91-4E9B-9DC5-1A0DADD7B10C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCF3E30B-940F-4DEF-A200-34E209DD80EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{59C96EEC-F89B-487C-82EC-7EC0DFF4A462}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="114">
   <si>
     <t>VCC</t>
   </si>
@@ -319,6 +319,63 @@
   </si>
   <si>
     <t>GPIO | TIM1CH2</t>
+  </si>
+  <si>
+    <t>Net Name</t>
+  </si>
+  <si>
+    <t>3.3V</t>
+  </si>
+  <si>
+    <t>AD1CH11</t>
+  </si>
+  <si>
+    <t>AD1CH3</t>
+  </si>
+  <si>
+    <t>AD1CH2</t>
+  </si>
+  <si>
+    <t>U1_RX</t>
+  </si>
+  <si>
+    <t>U1_TX</t>
+  </si>
+  <si>
+    <t>STRT_MEAS</t>
+  </si>
+  <si>
+    <t>SDA</t>
+  </si>
+  <si>
+    <t>SCL</t>
+  </si>
+  <si>
+    <t>RFIO antenna</t>
+  </si>
+  <si>
+    <t>RST net</t>
+  </si>
+  <si>
+    <t>BAT_COM</t>
+  </si>
+  <si>
+    <t>BAT_CHG</t>
+  </si>
+  <si>
+    <t>TIM1CH2</t>
+  </si>
+  <si>
+    <t>PWR_WKP</t>
+  </si>
+  <si>
+    <t>AD1CH0</t>
+  </si>
+  <si>
+    <t>DACOUT1</t>
+  </si>
+  <si>
+    <t>N/C</t>
   </si>
 </sst>
 </file>
@@ -420,13 +477,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
@@ -444,7 +501,7 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -453,10 +510,75 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
       <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
         <color indexed="64"/>
       </top>
       <bottom style="thin">
@@ -468,22 +590,22 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="medium">
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color indexed="64"/>
       </left>
-      <right style="thin">
+      <right style="medium">
         <color indexed="64"/>
       </right>
       <top style="thin">
@@ -492,71 +614,6 @@
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -568,18 +625,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -894,14 +951,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4ED2D8A3-3AD6-4717-8A34-86F977C7F915}">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="6" max="6" width="23.6640625" customWidth="1"/>
     <col min="7" max="7" width="35.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>46</v>
       </c>
@@ -917,15 +975,18 @@
       <c r="E1" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="7" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="5">
+      <c r="H1" s="12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -935,14 +996,17 @@
         <v>1</v>
       </c>
       <c r="D2" s="1"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="6" t="s">
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="8" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="5">
+      <c r="H2" s="13" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -952,14 +1016,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="1"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="6" t="s">
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="5">
+      <c r="H3" s="13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
@@ -974,15 +1041,18 @@
       <c r="E4" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="8" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="5">
+      <c r="H4" s="14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -997,15 +1067,18 @@
       <c r="E5" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="8" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="5">
+      <c r="H5" s="14" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -1014,19 +1087,22 @@
       <c r="C6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="13" t="s">
+      <c r="D6" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11" t="s">
+      <c r="E6" s="8"/>
+      <c r="F6" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="8" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="5">
+      <c r="H6" s="14" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7" s="4">
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -1035,19 +1111,22 @@
       <c r="C7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11" t="s">
+      <c r="E7" s="8"/>
+      <c r="F7" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="8" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="5">
+      <c r="H7" s="14" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" s="4">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -1056,19 +1135,22 @@
       <c r="C8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="11"/>
-      <c r="F8" s="11" t="s">
+      <c r="E8" s="8"/>
+      <c r="F8" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="8" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="5">
+      <c r="H8" s="14" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
@@ -1077,19 +1159,22 @@
       <c r="C9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="E9" s="11"/>
-      <c r="F9" s="11" t="s">
+      <c r="E9" s="8"/>
+      <c r="F9" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="8" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="5">
+      <c r="H9" s="14" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="4">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -1107,12 +1192,15 @@
       <c r="F10" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="8" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="5">
+      <c r="H10" s="14" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11" s="4">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -1130,12 +1218,15 @@
       <c r="F11" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="8" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="5">
+      <c r="H11" s="14" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" s="4">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -1147,16 +1238,19 @@
       <c r="D12" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11" t="s">
+      <c r="E12" s="8"/>
+      <c r="F12" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="8" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="5">
+      <c r="H12" s="14" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="4">
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
@@ -1165,19 +1259,22 @@
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="14" t="s">
+      <c r="D13" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11" t="s">
+      <c r="E13" s="8"/>
+      <c r="F13" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="8" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="5">
+      <c r="H13" s="14" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="4">
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -1186,19 +1283,22 @@
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11" t="s">
+      <c r="E14" s="8"/>
+      <c r="F14" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="8" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="5">
+      <c r="H14" s="14" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="4">
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
@@ -1208,14 +1308,17 @@
         <v>26</v>
       </c>
       <c r="D15" s="1"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="6" t="s">
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="5">
+      <c r="H15" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -1233,12 +1336,15 @@
       <c r="F16" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" s="8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="5">
+      <c r="H16" s="14" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
@@ -1248,14 +1354,17 @@
         <v>26</v>
       </c>
       <c r="D17" s="1"/>
-      <c r="E17" s="11"/>
-      <c r="F17" s="11"/>
-      <c r="G17" s="6" t="s">
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="5">
+      <c r="H17" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -1267,18 +1376,21 @@
       <c r="D18" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E18" s="11" t="s">
+      <c r="E18" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="F18" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="G18" s="8" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="5">
+      <c r="H18" s="14" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19" s="4">
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
@@ -1287,19 +1399,22 @@
       <c r="C19" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D19" s="14" t="s">
+      <c r="D19" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E19" s="11"/>
+      <c r="E19" s="8"/>
       <c r="F19" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="G19" s="8" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="5">
+      <c r="H19" s="14" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="4">
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -1308,19 +1423,22 @@
       <c r="C20" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="D20" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E20" s="11"/>
+      <c r="E20" s="8"/>
       <c r="F20" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="G20" s="8" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="5">
+      <c r="H20" s="14" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
@@ -1329,19 +1447,22 @@
       <c r="C21" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D21" s="14" t="s">
+      <c r="D21" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11" t="s">
+      <c r="E21" s="8"/>
+      <c r="F21" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="G21" s="6" t="s">
+      <c r="G21" s="8" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A22" s="5">
+      <c r="H21" s="14" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="4">
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
@@ -1350,19 +1471,22 @@
       <c r="C22" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D22" s="14" t="s">
+      <c r="D22" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11" t="s">
+      <c r="E22" s="8"/>
+      <c r="F22" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="G22" s="8" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="5">
+      <c r="H22" s="14" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="4">
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
@@ -1372,14 +1496,17 @@
         <v>26</v>
       </c>
       <c r="D23" s="1"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="6" t="s">
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="5">
+      <c r="H23" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A24" s="4">
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
@@ -1391,16 +1518,19 @@
       <c r="D24" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E24" s="11"/>
-      <c r="F24" s="11" t="s">
+      <c r="E24" s="8"/>
+      <c r="F24" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="G24" s="6" t="s">
+      <c r="G24" s="8" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="5">
+      <c r="H24" s="14" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A25" s="4">
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
@@ -1412,18 +1542,21 @@
       <c r="D25" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="E25" s="11" t="s">
+      <c r="E25" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="F25" s="11" t="s">
+      <c r="F25" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="G25" s="6" t="s">
+      <c r="G25" s="8" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="5">
+      <c r="H25" s="14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="4">
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
@@ -1432,21 +1565,24 @@
       <c r="C26" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D26" s="14" t="s">
+      <c r="D26" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="E26" s="11" t="s">
+      <c r="E26" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="F26" s="11" t="s">
+      <c r="F26" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="G26" s="6" t="s">
+      <c r="G26" s="8" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="5">
+      <c r="H26" s="14" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="4">
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
@@ -1458,18 +1594,21 @@
       <c r="D27" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E27" s="11" t="s">
+      <c r="E27" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="F27" s="11" t="s">
+      <c r="F27" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="G27" s="6" t="s">
+      <c r="G27" s="8" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="5">
+      <c r="H27" s="14" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="4">
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -1481,31 +1620,37 @@
       <c r="D28" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E28" s="11" t="s">
+      <c r="E28" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="F28" s="11" t="s">
+      <c r="F28" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="G28" s="8" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="7">
+      <c r="H28" s="14" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="5">
         <v>28</v>
       </c>
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C29" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D29" s="8"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
+      <c r="C29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="D29" s="6"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
       <c r="G29" s="9" t="s">
         <v>45</v>
+      </c>
+      <c r="H29" s="15" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>
